--- a/artfynd/A 39190-2024 artfynd.xlsx
+++ b/artfynd/A 39190-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120053484</v>
+        <v>120053329</v>
       </c>
       <c r="B2" t="n">
         <v>97907</v>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>584872</v>
+        <v>584784</v>
       </c>
       <c r="R2" t="n">
-        <v>6427608</v>
+        <v>6427617</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120053329</v>
+        <v>120053489</v>
       </c>
       <c r="B3" t="n">
         <v>97907</v>
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>584784</v>
+        <v>584861</v>
       </c>
       <c r="R3" t="n">
-        <v>6427617</v>
+        <v>6427606</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120053426</v>
+        <v>120053536</v>
       </c>
       <c r="B4" t="n">
         <v>97907</v>
@@ -945,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>584813</v>
+        <v>584842</v>
       </c>
       <c r="R4" t="n">
-        <v>6427608</v>
+        <v>6427616</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,7 +1008,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120053440</v>
+        <v>120053484</v>
       </c>
       <c r="B5" t="n">
         <v>97907</v>
@@ -1056,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>584826</v>
+        <v>584872</v>
       </c>
       <c r="R5" t="n">
-        <v>6427606</v>
+        <v>6427608</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120053519</v>
+        <v>120053492</v>
       </c>
       <c r="B6" t="n">
-        <v>57463</v>
+        <v>97907</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,39 +1131,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1171,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>584846</v>
+        <v>584850</v>
       </c>
       <c r="R6" t="n">
-        <v>6427613</v>
+        <v>6427616</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1215,6 +1211,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1233,7 +1230,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120053408</v>
+        <v>120053152</v>
       </c>
       <c r="B7" t="n">
         <v>97907</v>
@@ -1281,10 +1278,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>584804</v>
+        <v>584767</v>
       </c>
       <c r="R7" t="n">
-        <v>6427627</v>
+        <v>6427625</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1344,7 +1341,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120053152</v>
+        <v>120053408</v>
       </c>
       <c r="B8" t="n">
         <v>97907</v>
@@ -1392,10 +1389,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>584767</v>
+        <v>584804</v>
       </c>
       <c r="R8" t="n">
-        <v>6427625</v>
+        <v>6427627</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1455,7 +1452,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120053536</v>
+        <v>120053208</v>
       </c>
       <c r="B9" t="n">
         <v>97907</v>
@@ -1503,10 +1500,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>584842</v>
+        <v>584787</v>
       </c>
       <c r="R9" t="n">
-        <v>6427616</v>
+        <v>6427626</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1566,7 +1563,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120053208</v>
+        <v>120053426</v>
       </c>
       <c r="B10" t="n">
         <v>97907</v>
@@ -1614,10 +1611,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>584787</v>
+        <v>584813</v>
       </c>
       <c r="R10" t="n">
-        <v>6427626</v>
+        <v>6427608</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1788,10 +1785,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120053473</v>
+        <v>120053579</v>
       </c>
       <c r="B12" t="n">
-        <v>97907</v>
+        <v>91884</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1800,35 +1797,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>5449</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1836,10 +1836,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>584875</v>
+        <v>584845</v>
       </c>
       <c r="R12" t="n">
-        <v>6427605</v>
+        <v>6427617</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120053579</v>
+        <v>120053307</v>
       </c>
       <c r="B13" t="n">
-        <v>91884</v>
+        <v>97907</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1911,38 +1911,35 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5449</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1950,10 +1947,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>584845</v>
+        <v>584784</v>
       </c>
       <c r="R13" t="n">
-        <v>6427617</v>
+        <v>6427627</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2124,7 +2121,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120053307</v>
+        <v>120053440</v>
       </c>
       <c r="B15" t="n">
         <v>97907</v>
@@ -2172,10 +2169,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>584784</v>
+        <v>584826</v>
       </c>
       <c r="R15" t="n">
-        <v>6427627</v>
+        <v>6427606</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2235,7 +2232,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120053492</v>
+        <v>120053473</v>
       </c>
       <c r="B16" t="n">
         <v>97907</v>
@@ -2283,10 +2280,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>584850</v>
+        <v>584875</v>
       </c>
       <c r="R16" t="n">
-        <v>6427616</v>
+        <v>6427605</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2346,10 +2343,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120053489</v>
+        <v>120053519</v>
       </c>
       <c r="B17" t="n">
-        <v>97907</v>
+        <v>57463</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2358,35 +2355,39 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2394,10 +2395,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>584861</v>
+        <v>584846</v>
       </c>
       <c r="R17" t="n">
-        <v>6427606</v>
+        <v>6427613</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2438,7 +2439,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 39190-2024 artfynd.xlsx
+++ b/artfynd/A 39190-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120053329</v>
+        <v>120053484</v>
       </c>
       <c r="B2" t="n">
         <v>97907</v>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>584784</v>
+        <v>584872</v>
       </c>
       <c r="R2" t="n">
-        <v>6427617</v>
+        <v>6427608</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120053489</v>
+        <v>120053329</v>
       </c>
       <c r="B3" t="n">
         <v>97907</v>
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>584861</v>
+        <v>584784</v>
       </c>
       <c r="R3" t="n">
-        <v>6427606</v>
+        <v>6427617</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120053536</v>
+        <v>120053489</v>
       </c>
       <c r="B4" t="n">
         <v>97907</v>
@@ -945,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>584842</v>
+        <v>584861</v>
       </c>
       <c r="R4" t="n">
-        <v>6427616</v>
+        <v>6427606</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,7 +1008,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120053484</v>
+        <v>120053152</v>
       </c>
       <c r="B5" t="n">
         <v>97907</v>
@@ -1056,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>584872</v>
+        <v>584767</v>
       </c>
       <c r="R5" t="n">
-        <v>6427608</v>
+        <v>6427625</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1230,7 +1230,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120053152</v>
+        <v>120053161</v>
       </c>
       <c r="B7" t="n">
         <v>97907</v>
@@ -1278,10 +1278,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>584767</v>
+        <v>584785</v>
       </c>
       <c r="R7" t="n">
-        <v>6427625</v>
+        <v>6427627</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1452,7 +1452,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120053208</v>
+        <v>120053426</v>
       </c>
       <c r="B9" t="n">
         <v>97907</v>
@@ -1500,10 +1500,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>584787</v>
+        <v>584813</v>
       </c>
       <c r="R9" t="n">
-        <v>6427626</v>
+        <v>6427608</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1563,7 +1563,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120053426</v>
+        <v>120053440</v>
       </c>
       <c r="B10" t="n">
         <v>97907</v>
@@ -1611,10 +1611,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>584813</v>
+        <v>584826</v>
       </c>
       <c r="R10" t="n">
-        <v>6427608</v>
+        <v>6427606</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1674,7 +1674,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120053347</v>
+        <v>120053208</v>
       </c>
       <c r="B11" t="n">
         <v>97907</v>
@@ -1725,7 +1725,7 @@
         <v>584787</v>
       </c>
       <c r="R11" t="n">
-        <v>6427639</v>
+        <v>6427626</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1899,7 +1899,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120053307</v>
+        <v>120053473</v>
       </c>
       <c r="B13" t="n">
         <v>97907</v>
@@ -1947,10 +1947,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>584784</v>
+        <v>584875</v>
       </c>
       <c r="R13" t="n">
-        <v>6427627</v>
+        <v>6427605</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2010,10 +2010,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120053161</v>
+        <v>120053519</v>
       </c>
       <c r="B14" t="n">
-        <v>97907</v>
+        <v>57463</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2022,35 +2022,39 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2058,10 +2062,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>584785</v>
+        <v>584846</v>
       </c>
       <c r="R14" t="n">
-        <v>6427627</v>
+        <v>6427613</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2102,7 +2106,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2121,7 +2124,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120053440</v>
+        <v>120053307</v>
       </c>
       <c r="B15" t="n">
         <v>97907</v>
@@ -2169,10 +2172,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>584826</v>
+        <v>584784</v>
       </c>
       <c r="R15" t="n">
-        <v>6427606</v>
+        <v>6427627</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2232,7 +2235,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120053473</v>
+        <v>120053536</v>
       </c>
       <c r="B16" t="n">
         <v>97907</v>
@@ -2280,10 +2283,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>584875</v>
+        <v>584842</v>
       </c>
       <c r="R16" t="n">
-        <v>6427605</v>
+        <v>6427616</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2343,10 +2346,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120053519</v>
+        <v>120053347</v>
       </c>
       <c r="B17" t="n">
-        <v>57463</v>
+        <v>97907</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2355,39 +2358,35 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2395,10 +2394,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>584846</v>
+        <v>584787</v>
       </c>
       <c r="R17" t="n">
-        <v>6427613</v>
+        <v>6427639</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2439,6 +2438,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 39190-2024 artfynd.xlsx
+++ b/artfynd/A 39190-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120053484</v>
+        <v>120053208</v>
       </c>
       <c r="B2" t="n">
         <v>97907</v>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>584872</v>
+        <v>584787</v>
       </c>
       <c r="R2" t="n">
-        <v>6427608</v>
+        <v>6427626</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120053329</v>
+        <v>120053440</v>
       </c>
       <c r="B3" t="n">
         <v>97907</v>
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>584784</v>
+        <v>584826</v>
       </c>
       <c r="R3" t="n">
-        <v>6427617</v>
+        <v>6427606</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120053489</v>
+        <v>120053426</v>
       </c>
       <c r="B4" t="n">
         <v>97907</v>
@@ -945,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>584861</v>
+        <v>584813</v>
       </c>
       <c r="R4" t="n">
-        <v>6427606</v>
+        <v>6427608</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,7 +1008,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120053152</v>
+        <v>120053536</v>
       </c>
       <c r="B5" t="n">
         <v>97907</v>
@@ -1056,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>584767</v>
+        <v>584842</v>
       </c>
       <c r="R5" t="n">
-        <v>6427625</v>
+        <v>6427616</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,7 +1119,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120053492</v>
+        <v>120053408</v>
       </c>
       <c r="B6" t="n">
         <v>97907</v>
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>584850</v>
+        <v>584804</v>
       </c>
       <c r="R6" t="n">
-        <v>6427616</v>
+        <v>6427627</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,7 +1230,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120053161</v>
+        <v>120053152</v>
       </c>
       <c r="B7" t="n">
         <v>97907</v>
@@ -1278,10 +1278,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>584785</v>
+        <v>584767</v>
       </c>
       <c r="R7" t="n">
-        <v>6427627</v>
+        <v>6427625</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1341,7 +1341,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120053408</v>
+        <v>120053307</v>
       </c>
       <c r="B8" t="n">
         <v>97907</v>
@@ -1389,7 +1389,7 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>584804</v>
+        <v>584784</v>
       </c>
       <c r="R8" t="n">
         <v>6427627</v>
@@ -1452,7 +1452,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120053426</v>
+        <v>120053347</v>
       </c>
       <c r="B9" t="n">
         <v>97907</v>
@@ -1500,10 +1500,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>584813</v>
+        <v>584787</v>
       </c>
       <c r="R9" t="n">
-        <v>6427608</v>
+        <v>6427639</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1563,7 +1563,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120053440</v>
+        <v>120053473</v>
       </c>
       <c r="B10" t="n">
         <v>97907</v>
@@ -1611,10 +1611,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>584826</v>
+        <v>584875</v>
       </c>
       <c r="R10" t="n">
-        <v>6427606</v>
+        <v>6427605</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1674,7 +1674,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120053208</v>
+        <v>120053492</v>
       </c>
       <c r="B11" t="n">
         <v>97907</v>
@@ -1722,10 +1722,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>584787</v>
+        <v>584850</v>
       </c>
       <c r="R11" t="n">
-        <v>6427626</v>
+        <v>6427616</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1785,10 +1785,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120053579</v>
+        <v>120053489</v>
       </c>
       <c r="B12" t="n">
-        <v>91884</v>
+        <v>97907</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1797,38 +1797,35 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5449</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1836,10 +1833,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>584845</v>
+        <v>584861</v>
       </c>
       <c r="R12" t="n">
-        <v>6427617</v>
+        <v>6427606</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1899,7 +1896,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120053473</v>
+        <v>120053161</v>
       </c>
       <c r="B13" t="n">
         <v>97907</v>
@@ -1947,10 +1944,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>584875</v>
+        <v>584785</v>
       </c>
       <c r="R13" t="n">
-        <v>6427605</v>
+        <v>6427627</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2010,10 +2007,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120053519</v>
+        <v>120053579</v>
       </c>
       <c r="B14" t="n">
-        <v>57463</v>
+        <v>91884</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2026,35 +2023,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>5449</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2062,10 +2058,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>584846</v>
+        <v>584845</v>
       </c>
       <c r="R14" t="n">
-        <v>6427613</v>
+        <v>6427617</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2106,6 +2102,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2124,10 +2121,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120053307</v>
+        <v>120053519</v>
       </c>
       <c r="B15" t="n">
-        <v>97907</v>
+        <v>57463</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2136,35 +2133,39 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2172,10 +2173,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>584784</v>
+        <v>584846</v>
       </c>
       <c r="R15" t="n">
-        <v>6427627</v>
+        <v>6427613</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2216,7 +2217,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2235,7 +2235,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120053536</v>
+        <v>120053484</v>
       </c>
       <c r="B16" t="n">
         <v>97907</v>
@@ -2283,10 +2283,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>584842</v>
+        <v>584872</v>
       </c>
       <c r="R16" t="n">
-        <v>6427616</v>
+        <v>6427608</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2346,7 +2346,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120053347</v>
+        <v>120053329</v>
       </c>
       <c r="B17" t="n">
         <v>97907</v>
@@ -2394,10 +2394,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>584787</v>
+        <v>584784</v>
       </c>
       <c r="R17" t="n">
-        <v>6427639</v>
+        <v>6427617</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 39190-2024 artfynd.xlsx
+++ b/artfynd/A 39190-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120053208</v>
+        <v>120053329</v>
       </c>
       <c r="B2" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>584787</v>
+        <v>584784</v>
       </c>
       <c r="R2" t="n">
-        <v>6427626</v>
+        <v>6427617</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120053440</v>
+        <v>120053579</v>
       </c>
       <c r="B3" t="n">
-        <v>97907</v>
+        <v>91902</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,35 +798,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>5449</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -834,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>584826</v>
+        <v>584845</v>
       </c>
       <c r="R3" t="n">
-        <v>6427606</v>
+        <v>6427617</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120053426</v>
+        <v>120053484</v>
       </c>
       <c r="B4" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -945,7 +948,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>584813</v>
+        <v>584872</v>
       </c>
       <c r="R4" t="n">
         <v>6427608</v>
@@ -1008,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120053536</v>
+        <v>120053208</v>
       </c>
       <c r="B5" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1056,10 +1059,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>584842</v>
+        <v>584787</v>
       </c>
       <c r="R5" t="n">
-        <v>6427616</v>
+        <v>6427626</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120053408</v>
+        <v>120053161</v>
       </c>
       <c r="B6" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1167,7 +1170,7 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>584804</v>
+        <v>584785</v>
       </c>
       <c r="R6" t="n">
         <v>6427627</v>
@@ -1230,10 +1233,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120053152</v>
+        <v>120053519</v>
       </c>
       <c r="B7" t="n">
-        <v>97907</v>
+        <v>57473</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1242,35 +1245,39 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1278,10 +1285,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>584767</v>
+        <v>584846</v>
       </c>
       <c r="R7" t="n">
-        <v>6427625</v>
+        <v>6427613</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1322,7 +1329,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1341,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120053307</v>
+        <v>120053347</v>
       </c>
       <c r="B8" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1389,10 +1395,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>584784</v>
+        <v>584787</v>
       </c>
       <c r="R8" t="n">
-        <v>6427627</v>
+        <v>6427639</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1452,10 +1458,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120053347</v>
+        <v>120053307</v>
       </c>
       <c r="B9" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1500,10 +1506,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>584787</v>
+        <v>584784</v>
       </c>
       <c r="R9" t="n">
-        <v>6427639</v>
+        <v>6427627</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1563,10 +1569,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120053473</v>
+        <v>120053440</v>
       </c>
       <c r="B10" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1611,10 +1617,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>584875</v>
+        <v>584826</v>
       </c>
       <c r="R10" t="n">
-        <v>6427605</v>
+        <v>6427606</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1674,10 +1680,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120053492</v>
+        <v>120053426</v>
       </c>
       <c r="B11" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1722,10 +1728,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>584850</v>
+        <v>584813</v>
       </c>
       <c r="R11" t="n">
-        <v>6427616</v>
+        <v>6427608</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1788,7 +1794,7 @@
         <v>120053489</v>
       </c>
       <c r="B12" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1896,10 +1902,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120053161</v>
+        <v>120053408</v>
       </c>
       <c r="B13" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1944,7 +1950,7 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>584785</v>
+        <v>584804</v>
       </c>
       <c r="R13" t="n">
         <v>6427627</v>
@@ -2007,10 +2013,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120053579</v>
+        <v>120053492</v>
       </c>
       <c r="B14" t="n">
-        <v>91884</v>
+        <v>97930</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2019,38 +2025,35 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5449</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2058,10 +2061,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>584845</v>
+        <v>584850</v>
       </c>
       <c r="R14" t="n">
-        <v>6427617</v>
+        <v>6427616</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2121,10 +2124,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120053519</v>
+        <v>120053536</v>
       </c>
       <c r="B15" t="n">
-        <v>57463</v>
+        <v>97930</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2133,39 +2136,35 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2173,10 +2172,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>584846</v>
+        <v>584842</v>
       </c>
       <c r="R15" t="n">
-        <v>6427613</v>
+        <v>6427616</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2217,6 +2216,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2235,10 +2235,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120053484</v>
+        <v>120053152</v>
       </c>
       <c r="B16" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2283,10 +2283,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>584872</v>
+        <v>584767</v>
       </c>
       <c r="R16" t="n">
-        <v>6427608</v>
+        <v>6427625</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2346,10 +2346,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120053329</v>
+        <v>120053473</v>
       </c>
       <c r="B17" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2394,10 +2394,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>584784</v>
+        <v>584875</v>
       </c>
       <c r="R17" t="n">
-        <v>6427617</v>
+        <v>6427605</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 39190-2024 artfynd.xlsx
+++ b/artfynd/A 39190-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120053329</v>
+        <v>120053484</v>
       </c>
       <c r="B2" t="n">
         <v>97930</v>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>584784</v>
+        <v>584872</v>
       </c>
       <c r="R2" t="n">
-        <v>6427617</v>
+        <v>6427608</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120053579</v>
+        <v>120053208</v>
       </c>
       <c r="B3" t="n">
-        <v>91902</v>
+        <v>97930</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,38 +798,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5449</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -837,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>584845</v>
+        <v>584787</v>
       </c>
       <c r="R3" t="n">
-        <v>6427617</v>
+        <v>6427626</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -900,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120053484</v>
+        <v>120053426</v>
       </c>
       <c r="B4" t="n">
         <v>97930</v>
@@ -948,7 +945,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>584872</v>
+        <v>584813</v>
       </c>
       <c r="R4" t="n">
         <v>6427608</v>
@@ -1011,7 +1008,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120053208</v>
+        <v>120053329</v>
       </c>
       <c r="B5" t="n">
         <v>97930</v>
@@ -1059,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>584787</v>
+        <v>584784</v>
       </c>
       <c r="R5" t="n">
-        <v>6427626</v>
+        <v>6427617</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1122,7 +1119,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120053161</v>
+        <v>120053440</v>
       </c>
       <c r="B6" t="n">
         <v>97930</v>
@@ -1170,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>584785</v>
+        <v>584826</v>
       </c>
       <c r="R6" t="n">
-        <v>6427627</v>
+        <v>6427606</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1347,7 +1344,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120053347</v>
+        <v>120053489</v>
       </c>
       <c r="B8" t="n">
         <v>97930</v>
@@ -1395,10 +1392,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>584787</v>
+        <v>584861</v>
       </c>
       <c r="R8" t="n">
-        <v>6427639</v>
+        <v>6427606</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1458,7 +1455,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120053307</v>
+        <v>120053161</v>
       </c>
       <c r="B9" t="n">
         <v>97930</v>
@@ -1506,7 +1503,7 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>584784</v>
+        <v>584785</v>
       </c>
       <c r="R9" t="n">
         <v>6427627</v>
@@ -1569,7 +1566,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120053440</v>
+        <v>120053492</v>
       </c>
       <c r="B10" t="n">
         <v>97930</v>
@@ -1617,10 +1614,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>584826</v>
+        <v>584850</v>
       </c>
       <c r="R10" t="n">
-        <v>6427606</v>
+        <v>6427616</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1680,7 +1677,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120053426</v>
+        <v>120053473</v>
       </c>
       <c r="B11" t="n">
         <v>97930</v>
@@ -1728,10 +1725,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>584813</v>
+        <v>584875</v>
       </c>
       <c r="R11" t="n">
-        <v>6427608</v>
+        <v>6427605</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1791,7 +1788,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120053489</v>
+        <v>120053347</v>
       </c>
       <c r="B12" t="n">
         <v>97930</v>
@@ -1839,10 +1836,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>584861</v>
+        <v>584787</v>
       </c>
       <c r="R12" t="n">
-        <v>6427606</v>
+        <v>6427639</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1902,10 +1899,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120053408</v>
+        <v>120053579</v>
       </c>
       <c r="B13" t="n">
-        <v>97930</v>
+        <v>91902</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1914,35 +1911,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>5449</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1950,10 +1950,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>584804</v>
+        <v>584845</v>
       </c>
       <c r="R13" t="n">
-        <v>6427627</v>
+        <v>6427617</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2013,7 +2013,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120053492</v>
+        <v>120053408</v>
       </c>
       <c r="B14" t="n">
         <v>97930</v>
@@ -2061,10 +2061,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>584850</v>
+        <v>584804</v>
       </c>
       <c r="R14" t="n">
-        <v>6427616</v>
+        <v>6427627</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2124,7 +2124,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120053536</v>
+        <v>120053307</v>
       </c>
       <c r="B15" t="n">
         <v>97930</v>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>584842</v>
+        <v>584784</v>
       </c>
       <c r="R15" t="n">
-        <v>6427616</v>
+        <v>6427627</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2346,7 +2346,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120053473</v>
+        <v>120053536</v>
       </c>
       <c r="B17" t="n">
         <v>97930</v>
@@ -2394,10 +2394,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>584875</v>
+        <v>584842</v>
       </c>
       <c r="R17" t="n">
-        <v>6427605</v>
+        <v>6427616</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 39190-2024 artfynd.xlsx
+++ b/artfynd/A 39190-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120053484</v>
+        <v>120053473</v>
       </c>
       <c r="B2" t="n">
         <v>97930</v>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>584872</v>
+        <v>584875</v>
       </c>
       <c r="R2" t="n">
-        <v>6427608</v>
+        <v>6427605</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120053208</v>
+        <v>120053579</v>
       </c>
       <c r="B3" t="n">
-        <v>97930</v>
+        <v>91902</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,35 +798,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>5449</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -834,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>584787</v>
+        <v>584845</v>
       </c>
       <c r="R3" t="n">
-        <v>6427626</v>
+        <v>6427617</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,7 +900,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120053426</v>
+        <v>120053152</v>
       </c>
       <c r="B4" t="n">
         <v>97930</v>
@@ -945,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>584813</v>
+        <v>584767</v>
       </c>
       <c r="R4" t="n">
-        <v>6427608</v>
+        <v>6427625</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,7 +1011,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120053329</v>
+        <v>120053536</v>
       </c>
       <c r="B5" t="n">
         <v>97930</v>
@@ -1056,10 +1059,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>584784</v>
+        <v>584842</v>
       </c>
       <c r="R5" t="n">
-        <v>6427617</v>
+        <v>6427616</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,7 +1122,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120053440</v>
+        <v>120053208</v>
       </c>
       <c r="B6" t="n">
         <v>97930</v>
@@ -1167,10 +1170,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>584826</v>
+        <v>584787</v>
       </c>
       <c r="R6" t="n">
-        <v>6427606</v>
+        <v>6427626</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1344,7 +1347,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120053489</v>
+        <v>120053426</v>
       </c>
       <c r="B8" t="n">
         <v>97930</v>
@@ -1392,10 +1395,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>584861</v>
+        <v>584813</v>
       </c>
       <c r="R8" t="n">
-        <v>6427606</v>
+        <v>6427608</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1455,7 +1458,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120053161</v>
+        <v>120053489</v>
       </c>
       <c r="B9" t="n">
         <v>97930</v>
@@ -1503,10 +1506,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>584785</v>
+        <v>584861</v>
       </c>
       <c r="R9" t="n">
-        <v>6427627</v>
+        <v>6427606</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1566,7 +1569,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120053492</v>
+        <v>120053347</v>
       </c>
       <c r="B10" t="n">
         <v>97930</v>
@@ -1614,10 +1617,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>584850</v>
+        <v>584787</v>
       </c>
       <c r="R10" t="n">
-        <v>6427616</v>
+        <v>6427639</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1677,7 +1680,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120053473</v>
+        <v>120053161</v>
       </c>
       <c r="B11" t="n">
         <v>97930</v>
@@ -1725,10 +1728,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>584875</v>
+        <v>584785</v>
       </c>
       <c r="R11" t="n">
-        <v>6427605</v>
+        <v>6427627</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1788,7 +1791,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120053347</v>
+        <v>120053408</v>
       </c>
       <c r="B12" t="n">
         <v>97930</v>
@@ -1836,10 +1839,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>584787</v>
+        <v>584804</v>
       </c>
       <c r="R12" t="n">
-        <v>6427639</v>
+        <v>6427627</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1899,10 +1902,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120053579</v>
+        <v>120053329</v>
       </c>
       <c r="B13" t="n">
-        <v>91902</v>
+        <v>97930</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1911,38 +1914,35 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5449</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1950,7 +1950,7 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>584845</v>
+        <v>584784</v>
       </c>
       <c r="R13" t="n">
         <v>6427617</v>
@@ -2013,7 +2013,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120053408</v>
+        <v>120053492</v>
       </c>
       <c r="B14" t="n">
         <v>97930</v>
@@ -2061,10 +2061,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>584804</v>
+        <v>584850</v>
       </c>
       <c r="R14" t="n">
-        <v>6427627</v>
+        <v>6427616</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2124,7 +2124,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120053307</v>
+        <v>120053440</v>
       </c>
       <c r="B15" t="n">
         <v>97930</v>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>584784</v>
+        <v>584826</v>
       </c>
       <c r="R15" t="n">
-        <v>6427627</v>
+        <v>6427606</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2235,7 +2235,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120053152</v>
+        <v>120053307</v>
       </c>
       <c r="B16" t="n">
         <v>97930</v>
@@ -2283,10 +2283,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>584767</v>
+        <v>584784</v>
       </c>
       <c r="R16" t="n">
-        <v>6427625</v>
+        <v>6427627</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2346,7 +2346,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120053536</v>
+        <v>120053484</v>
       </c>
       <c r="B17" t="n">
         <v>97930</v>
@@ -2394,10 +2394,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>584842</v>
+        <v>584872</v>
       </c>
       <c r="R17" t="n">
-        <v>6427616</v>
+        <v>6427608</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 39190-2024 artfynd.xlsx
+++ b/artfynd/A 39190-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120053473</v>
+        <v>120053426</v>
       </c>
       <c r="B2" t="n">
         <v>97930</v>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>584875</v>
+        <v>584813</v>
       </c>
       <c r="R2" t="n">
-        <v>6427605</v>
+        <v>6427608</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120053579</v>
+        <v>120053161</v>
       </c>
       <c r="B3" t="n">
-        <v>91902</v>
+        <v>97930</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,38 +798,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5449</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -837,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>584845</v>
+        <v>584785</v>
       </c>
       <c r="R3" t="n">
-        <v>6427617</v>
+        <v>6427627</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -900,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120053152</v>
+        <v>120053489</v>
       </c>
       <c r="B4" t="n">
         <v>97930</v>
@@ -948,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>584767</v>
+        <v>584861</v>
       </c>
       <c r="R4" t="n">
-        <v>6427625</v>
+        <v>6427606</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1011,7 +1008,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120053536</v>
+        <v>120053152</v>
       </c>
       <c r="B5" t="n">
         <v>97930</v>
@@ -1059,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>584842</v>
+        <v>584767</v>
       </c>
       <c r="R5" t="n">
-        <v>6427616</v>
+        <v>6427625</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1233,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120053519</v>
+        <v>120053484</v>
       </c>
       <c r="B7" t="n">
-        <v>57473</v>
+        <v>97930</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1245,39 +1242,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1285,10 +1278,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>584846</v>
+        <v>584872</v>
       </c>
       <c r="R7" t="n">
-        <v>6427613</v>
+        <v>6427608</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1329,6 +1322,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1347,7 +1341,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120053426</v>
+        <v>120053307</v>
       </c>
       <c r="B8" t="n">
         <v>97930</v>
@@ -1395,10 +1389,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>584813</v>
+        <v>584784</v>
       </c>
       <c r="R8" t="n">
-        <v>6427608</v>
+        <v>6427627</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1458,7 +1452,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120053489</v>
+        <v>120053492</v>
       </c>
       <c r="B9" t="n">
         <v>97930</v>
@@ -1506,10 +1500,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>584861</v>
+        <v>584850</v>
       </c>
       <c r="R9" t="n">
-        <v>6427606</v>
+        <v>6427616</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1569,10 +1563,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120053347</v>
+        <v>120053519</v>
       </c>
       <c r="B10" t="n">
-        <v>97930</v>
+        <v>57473</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1581,35 +1575,39 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1617,10 +1615,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>584787</v>
+        <v>584846</v>
       </c>
       <c r="R10" t="n">
-        <v>6427639</v>
+        <v>6427613</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1661,7 +1659,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1680,7 +1677,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120053161</v>
+        <v>120053329</v>
       </c>
       <c r="B11" t="n">
         <v>97930</v>
@@ -1728,10 +1725,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>584785</v>
+        <v>584784</v>
       </c>
       <c r="R11" t="n">
-        <v>6427627</v>
+        <v>6427617</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1791,7 +1788,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120053408</v>
+        <v>120053536</v>
       </c>
       <c r="B12" t="n">
         <v>97930</v>
@@ -1839,10 +1836,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>584804</v>
+        <v>584842</v>
       </c>
       <c r="R12" t="n">
-        <v>6427627</v>
+        <v>6427616</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1902,10 +1899,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120053329</v>
+        <v>120053579</v>
       </c>
       <c r="B13" t="n">
-        <v>97930</v>
+        <v>91902</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1914,35 +1911,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>5449</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1950,7 +1950,7 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>584784</v>
+        <v>584845</v>
       </c>
       <c r="R13" t="n">
         <v>6427617</v>
@@ -2013,7 +2013,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120053492</v>
+        <v>120053408</v>
       </c>
       <c r="B14" t="n">
         <v>97930</v>
@@ -2061,10 +2061,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>584850</v>
+        <v>584804</v>
       </c>
       <c r="R14" t="n">
-        <v>6427616</v>
+        <v>6427627</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2235,7 +2235,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120053307</v>
+        <v>120053473</v>
       </c>
       <c r="B16" t="n">
         <v>97930</v>
@@ -2283,10 +2283,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>584784</v>
+        <v>584875</v>
       </c>
       <c r="R16" t="n">
-        <v>6427627</v>
+        <v>6427605</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2346,7 +2346,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120053484</v>
+        <v>120053347</v>
       </c>
       <c r="B17" t="n">
         <v>97930</v>
@@ -2394,10 +2394,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>584872</v>
+        <v>584787</v>
       </c>
       <c r="R17" t="n">
-        <v>6427608</v>
+        <v>6427639</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 39190-2024 artfynd.xlsx
+++ b/artfynd/A 39190-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120053426</v>
+        <v>120053440</v>
       </c>
       <c r="B2" t="n">
         <v>97930</v>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>584813</v>
+        <v>584826</v>
       </c>
       <c r="R2" t="n">
-        <v>6427608</v>
+        <v>6427606</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120053161</v>
+        <v>120053152</v>
       </c>
       <c r="B3" t="n">
         <v>97930</v>
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>584785</v>
+        <v>584767</v>
       </c>
       <c r="R3" t="n">
-        <v>6427627</v>
+        <v>6427625</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120053489</v>
+        <v>120053408</v>
       </c>
       <c r="B4" t="n">
         <v>97930</v>
@@ -945,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>584861</v>
+        <v>584804</v>
       </c>
       <c r="R4" t="n">
-        <v>6427606</v>
+        <v>6427627</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,7 +1008,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120053152</v>
+        <v>120053161</v>
       </c>
       <c r="B5" t="n">
         <v>97930</v>
@@ -1056,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>584767</v>
+        <v>584785</v>
       </c>
       <c r="R5" t="n">
-        <v>6427625</v>
+        <v>6427627</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,7 +1119,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120053208</v>
+        <v>120053347</v>
       </c>
       <c r="B6" t="n">
         <v>97930</v>
@@ -1170,7 +1170,7 @@
         <v>584787</v>
       </c>
       <c r="R6" t="n">
-        <v>6427626</v>
+        <v>6427639</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,7 +1230,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120053484</v>
+        <v>120053536</v>
       </c>
       <c r="B7" t="n">
         <v>97930</v>
@@ -1278,10 +1278,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>584872</v>
+        <v>584842</v>
       </c>
       <c r="R7" t="n">
-        <v>6427608</v>
+        <v>6427616</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1452,7 +1452,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120053492</v>
+        <v>120053426</v>
       </c>
       <c r="B9" t="n">
         <v>97930</v>
@@ -1500,10 +1500,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>584850</v>
+        <v>584813</v>
       </c>
       <c r="R9" t="n">
-        <v>6427616</v>
+        <v>6427608</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1677,7 +1677,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120053329</v>
+        <v>120053208</v>
       </c>
       <c r="B11" t="n">
         <v>97930</v>
@@ -1725,10 +1725,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>584784</v>
+        <v>584787</v>
       </c>
       <c r="R11" t="n">
-        <v>6427617</v>
+        <v>6427626</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1788,7 +1788,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120053536</v>
+        <v>120053329</v>
       </c>
       <c r="B12" t="n">
         <v>97930</v>
@@ -1836,10 +1836,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>584842</v>
+        <v>584784</v>
       </c>
       <c r="R12" t="n">
-        <v>6427616</v>
+        <v>6427617</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120053579</v>
+        <v>120053484</v>
       </c>
       <c r="B13" t="n">
-        <v>91902</v>
+        <v>97930</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1911,38 +1911,35 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5449</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1950,10 +1947,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>584845</v>
+        <v>584872</v>
       </c>
       <c r="R13" t="n">
-        <v>6427617</v>
+        <v>6427608</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2013,10 +2010,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120053408</v>
+        <v>120053579</v>
       </c>
       <c r="B14" t="n">
-        <v>97930</v>
+        <v>91902</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2025,35 +2022,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>5449</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2061,10 +2061,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>584804</v>
+        <v>584845</v>
       </c>
       <c r="R14" t="n">
-        <v>6427627</v>
+        <v>6427617</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2124,7 +2124,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120053440</v>
+        <v>120053489</v>
       </c>
       <c r="B15" t="n">
         <v>97930</v>
@@ -2172,7 +2172,7 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>584826</v>
+        <v>584861</v>
       </c>
       <c r="R15" t="n">
         <v>6427606</v>
@@ -2235,7 +2235,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120053473</v>
+        <v>120053492</v>
       </c>
       <c r="B16" t="n">
         <v>97930</v>
@@ -2283,10 +2283,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>584875</v>
+        <v>584850</v>
       </c>
       <c r="R16" t="n">
-        <v>6427605</v>
+        <v>6427616</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2346,7 +2346,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120053347</v>
+        <v>120053473</v>
       </c>
       <c r="B17" t="n">
         <v>97930</v>
@@ -2394,10 +2394,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>584787</v>
+        <v>584875</v>
       </c>
       <c r="R17" t="n">
-        <v>6427639</v>
+        <v>6427605</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 39190-2024 artfynd.xlsx
+++ b/artfynd/A 39190-2024 artfynd.xlsx
@@ -1230,7 +1230,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120053536</v>
+        <v>120053307</v>
       </c>
       <c r="B7" t="n">
         <v>97930</v>
@@ -1278,10 +1278,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>584842</v>
+        <v>584784</v>
       </c>
       <c r="R7" t="n">
-        <v>6427616</v>
+        <v>6427627</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1341,7 +1341,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120053307</v>
+        <v>120053536</v>
       </c>
       <c r="B8" t="n">
         <v>97930</v>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>584784</v>
+        <v>584842</v>
       </c>
       <c r="R8" t="n">
-        <v>6427627</v>
+        <v>6427616</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 39190-2024 artfynd.xlsx
+++ b/artfynd/A 39190-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120053440</v>
+        <v>120053536</v>
       </c>
       <c r="B2" t="n">
         <v>97930</v>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>584826</v>
+        <v>584842</v>
       </c>
       <c r="R2" t="n">
-        <v>6427606</v>
+        <v>6427616</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120053152</v>
+        <v>120053161</v>
       </c>
       <c r="B3" t="n">
         <v>97930</v>
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>584767</v>
+        <v>584785</v>
       </c>
       <c r="R3" t="n">
-        <v>6427625</v>
+        <v>6427627</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1008,7 +1008,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120053161</v>
+        <v>120053307</v>
       </c>
       <c r="B5" t="n">
         <v>97930</v>
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>584785</v>
+        <v>584784</v>
       </c>
       <c r="R5" t="n">
         <v>6427627</v>
@@ -1230,7 +1230,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120053307</v>
+        <v>120053208</v>
       </c>
       <c r="B7" t="n">
         <v>97930</v>
@@ -1278,10 +1278,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>584784</v>
+        <v>584787</v>
       </c>
       <c r="R7" t="n">
-        <v>6427627</v>
+        <v>6427626</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1341,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120053536</v>
+        <v>120053519</v>
       </c>
       <c r="B8" t="n">
-        <v>97930</v>
+        <v>57473</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1353,35 +1353,39 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1389,10 +1393,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>584842</v>
+        <v>584846</v>
       </c>
       <c r="R8" t="n">
-        <v>6427616</v>
+        <v>6427613</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1433,7 +1437,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1452,7 +1455,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120053426</v>
+        <v>120053484</v>
       </c>
       <c r="B9" t="n">
         <v>97930</v>
@@ -1500,7 +1503,7 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>584813</v>
+        <v>584872</v>
       </c>
       <c r="R9" t="n">
         <v>6427608</v>
@@ -1563,10 +1566,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120053519</v>
+        <v>120053440</v>
       </c>
       <c r="B10" t="n">
-        <v>57473</v>
+        <v>97930</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1575,39 +1578,35 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1615,10 +1614,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>584846</v>
+        <v>584826</v>
       </c>
       <c r="R10" t="n">
-        <v>6427613</v>
+        <v>6427606</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1659,6 +1658,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1677,7 +1677,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120053208</v>
+        <v>120053426</v>
       </c>
       <c r="B11" t="n">
         <v>97930</v>
@@ -1725,10 +1725,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>584787</v>
+        <v>584813</v>
       </c>
       <c r="R11" t="n">
-        <v>6427626</v>
+        <v>6427608</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1788,7 +1788,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120053329</v>
+        <v>120053489</v>
       </c>
       <c r="B12" t="n">
         <v>97930</v>
@@ -1836,10 +1836,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>584784</v>
+        <v>584861</v>
       </c>
       <c r="R12" t="n">
-        <v>6427617</v>
+        <v>6427606</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1899,7 +1899,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120053484</v>
+        <v>120053329</v>
       </c>
       <c r="B13" t="n">
         <v>97930</v>
@@ -1947,10 +1947,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>584872</v>
+        <v>584784</v>
       </c>
       <c r="R13" t="n">
-        <v>6427608</v>
+        <v>6427617</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2124,7 +2124,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120053489</v>
+        <v>120053473</v>
       </c>
       <c r="B15" t="n">
         <v>97930</v>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>584861</v>
+        <v>584875</v>
       </c>
       <c r="R15" t="n">
-        <v>6427606</v>
+        <v>6427605</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2346,7 +2346,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120053473</v>
+        <v>120053152</v>
       </c>
       <c r="B17" t="n">
         <v>97930</v>
@@ -2394,10 +2394,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>584875</v>
+        <v>584767</v>
       </c>
       <c r="R17" t="n">
-        <v>6427605</v>
+        <v>6427625</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 39190-2024 artfynd.xlsx
+++ b/artfynd/A 39190-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120053536</v>
+        <v>120053347</v>
       </c>
       <c r="B2" t="n">
         <v>97930</v>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>584842</v>
+        <v>584787</v>
       </c>
       <c r="R2" t="n">
-        <v>6427616</v>
+        <v>6427639</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120053161</v>
+        <v>120053426</v>
       </c>
       <c r="B3" t="n">
         <v>97930</v>
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>584785</v>
+        <v>584813</v>
       </c>
       <c r="R3" t="n">
-        <v>6427627</v>
+        <v>6427608</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1008,7 +1008,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120053307</v>
+        <v>120053329</v>
       </c>
       <c r="B5" t="n">
         <v>97930</v>
@@ -1059,7 +1059,7 @@
         <v>584784</v>
       </c>
       <c r="R5" t="n">
-        <v>6427627</v>
+        <v>6427617</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,7 +1119,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120053347</v>
+        <v>120053307</v>
       </c>
       <c r="B6" t="n">
         <v>97930</v>
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>584787</v>
+        <v>584784</v>
       </c>
       <c r="R6" t="n">
-        <v>6427639</v>
+        <v>6427627</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,7 +1230,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120053208</v>
+        <v>120053536</v>
       </c>
       <c r="B7" t="n">
         <v>97930</v>
@@ -1278,10 +1278,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>584787</v>
+        <v>584842</v>
       </c>
       <c r="R7" t="n">
-        <v>6427626</v>
+        <v>6427616</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1341,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120053519</v>
+        <v>120053152</v>
       </c>
       <c r="B8" t="n">
-        <v>57473</v>
+        <v>97930</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1353,39 +1353,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1393,10 +1389,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>584846</v>
+        <v>584767</v>
       </c>
       <c r="R8" t="n">
-        <v>6427613</v>
+        <v>6427625</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1437,6 +1433,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1455,7 +1452,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120053484</v>
+        <v>120053161</v>
       </c>
       <c r="B9" t="n">
         <v>97930</v>
@@ -1503,10 +1500,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>584872</v>
+        <v>584785</v>
       </c>
       <c r="R9" t="n">
-        <v>6427608</v>
+        <v>6427627</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1566,7 +1563,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120053440</v>
+        <v>120053492</v>
       </c>
       <c r="B10" t="n">
         <v>97930</v>
@@ -1614,10 +1611,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>584826</v>
+        <v>584850</v>
       </c>
       <c r="R10" t="n">
-        <v>6427606</v>
+        <v>6427616</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1677,7 +1674,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120053426</v>
+        <v>120053208</v>
       </c>
       <c r="B11" t="n">
         <v>97930</v>
@@ -1725,10 +1722,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>584813</v>
+        <v>584787</v>
       </c>
       <c r="R11" t="n">
-        <v>6427608</v>
+        <v>6427626</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1788,7 +1785,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120053489</v>
+        <v>120053473</v>
       </c>
       <c r="B12" t="n">
         <v>97930</v>
@@ -1836,10 +1833,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>584861</v>
+        <v>584875</v>
       </c>
       <c r="R12" t="n">
-        <v>6427606</v>
+        <v>6427605</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1899,10 +1896,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120053329</v>
+        <v>120053579</v>
       </c>
       <c r="B13" t="n">
-        <v>97930</v>
+        <v>91902</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1911,35 +1908,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>5449</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>584784</v>
+        <v>584845</v>
       </c>
       <c r="R13" t="n">
         <v>6427617</v>
@@ -2010,10 +2010,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120053579</v>
+        <v>120053519</v>
       </c>
       <c r="B14" t="n">
-        <v>91902</v>
+        <v>57473</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2026,34 +2026,35 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5449</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2061,10 +2062,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>584845</v>
+        <v>584846</v>
       </c>
       <c r="R14" t="n">
-        <v>6427617</v>
+        <v>6427613</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2105,7 +2106,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2124,7 +2124,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120053473</v>
+        <v>120053489</v>
       </c>
       <c r="B15" t="n">
         <v>97930</v>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>584875</v>
+        <v>584861</v>
       </c>
       <c r="R15" t="n">
-        <v>6427605</v>
+        <v>6427606</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2235,7 +2235,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120053492</v>
+        <v>120053484</v>
       </c>
       <c r="B16" t="n">
         <v>97930</v>
@@ -2283,10 +2283,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>584850</v>
+        <v>584872</v>
       </c>
       <c r="R16" t="n">
-        <v>6427616</v>
+        <v>6427608</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2346,7 +2346,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120053152</v>
+        <v>120053440</v>
       </c>
       <c r="B17" t="n">
         <v>97930</v>
@@ -2394,10 +2394,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>584767</v>
+        <v>584826</v>
       </c>
       <c r="R17" t="n">
-        <v>6427625</v>
+        <v>6427606</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 39190-2024 artfynd.xlsx
+++ b/artfynd/A 39190-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,47 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120053329</v>
+        <v>120053593</v>
       </c>
       <c r="B2" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93193</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>4363</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Pers.) Banker</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +721,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>584784</v>
+        <v>584863</v>
       </c>
       <c r="R2" t="n">
-        <v>6427617</v>
+        <v>6427635</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,47 +784,46 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120053492</v>
+        <v>120053519</v>
       </c>
       <c r="B3" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -834,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>584850</v>
+        <v>584846</v>
       </c>
       <c r="R3" t="n">
-        <v>6427616</v>
+        <v>6427613</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -878,7 +875,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -897,51 +893,42 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120053519</v>
+        <v>120053152</v>
       </c>
       <c r="B4" t="n">
-        <v>57473</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -949,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>584846</v>
+        <v>584767</v>
       </c>
       <c r="R4" t="n">
-        <v>6427613</v>
+        <v>6427625</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,6 +980,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1011,50 +999,42 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120053579</v>
+        <v>120053161</v>
       </c>
       <c r="B5" t="n">
-        <v>91902</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5449</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1062,10 +1042,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>584845</v>
+        <v>584785</v>
       </c>
       <c r="R5" t="n">
-        <v>6427617</v>
+        <v>6427627</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1125,15 +1105,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120053426</v>
+        <v>120053208</v>
       </c>
       <c r="B6" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,10 +1148,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>584813</v>
+        <v>584787</v>
       </c>
       <c r="R6" t="n">
-        <v>6427608</v>
+        <v>6427626</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1239,12 +1214,7 @@
         <v>120053307</v>
       </c>
       <c r="B7" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1347,15 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120053473</v>
+        <v>120053329</v>
       </c>
       <c r="B8" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1395,10 +1360,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>584875</v>
+        <v>584784</v>
       </c>
       <c r="R8" t="n">
-        <v>6427605</v>
+        <v>6427617</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1458,15 +1423,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120053161</v>
+        <v>120053347</v>
       </c>
       <c r="B9" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1506,10 +1466,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>584785</v>
+        <v>584787</v>
       </c>
       <c r="R9" t="n">
-        <v>6427627</v>
+        <v>6427639</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1569,15 +1529,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120053484</v>
+        <v>120053355</v>
       </c>
       <c r="B10" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1617,10 +1572,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>584872</v>
+        <v>584798</v>
       </c>
       <c r="R10" t="n">
-        <v>6427608</v>
+        <v>6427643</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1680,15 +1635,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120053208</v>
+        <v>120053381</v>
       </c>
       <c r="B11" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1728,10 +1678,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>584787</v>
+        <v>584803</v>
       </c>
       <c r="R11" t="n">
-        <v>6427626</v>
+        <v>6427636</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1791,15 +1741,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120053347</v>
+        <v>120053408</v>
       </c>
       <c r="B12" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1839,10 +1784,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>584787</v>
+        <v>584804</v>
       </c>
       <c r="R12" t="n">
-        <v>6427639</v>
+        <v>6427627</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1902,15 +1847,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120053440</v>
+        <v>120053426</v>
       </c>
       <c r="B13" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1950,10 +1890,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>584826</v>
+        <v>584813</v>
       </c>
       <c r="R13" t="n">
-        <v>6427606</v>
+        <v>6427608</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2013,15 +1953,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120053152</v>
+        <v>120053440</v>
       </c>
       <c r="B14" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2061,10 +1996,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>584767</v>
+        <v>584826</v>
       </c>
       <c r="R14" t="n">
-        <v>6427625</v>
+        <v>6427606</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2124,15 +2059,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120053536</v>
+        <v>120053453</v>
       </c>
       <c r="B15" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2175,7 +2105,7 @@
         <v>584842</v>
       </c>
       <c r="R15" t="n">
-        <v>6427616</v>
+        <v>6427561</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2235,15 +2165,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120053489</v>
+        <v>120053463</v>
       </c>
       <c r="B16" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2283,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>584861</v>
+        <v>584850</v>
       </c>
       <c r="R16" t="n">
-        <v>6427606</v>
+        <v>6427577</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2346,15 +2271,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120053408</v>
+        <v>120053466</v>
       </c>
       <c r="B17" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2394,10 +2314,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>584804</v>
+        <v>584874</v>
       </c>
       <c r="R17" t="n">
-        <v>6427627</v>
+        <v>6427584</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2454,6 +2374,854 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>120053473</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>A 39190, Härnum, Sm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>584875</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6427605</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Västra Ed</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-09-27</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-09-27</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>120053484</v>
+      </c>
+      <c r="B19" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>A 39190, Härnum, Sm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>584872</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6427608</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Västra Ed</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-09-27</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-09-27</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>120053489</v>
+      </c>
+      <c r="B20" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>A 39190, Härnum, Sm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>584861</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6427606</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Västra Ed</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-09-27</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-09-27</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>120053492</v>
+      </c>
+      <c r="B21" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>A 39190, Härnum, Sm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>584850</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6427616</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Västra Ed</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-09-27</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-09-27</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>120053536</v>
+      </c>
+      <c r="B22" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>A 39190, Härnum, Sm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>584842</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6427616</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Västra Ed</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-09-27</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-09-27</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>120053783</v>
+      </c>
+      <c r="B23" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>A 39190, Härnum, Sm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>584796</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6427644</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Västra Ed</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-09-27</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-09-27</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>120053792</v>
+      </c>
+      <c r="B24" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>A 39190, Härnum, Sm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>584799</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6427638</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Västra Ed</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-09-27</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-09-27</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>120053801</v>
+      </c>
+      <c r="B25" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>A 39190, Härnum, Sm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>584808</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6427637</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Västra Ed</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-09-27</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-09-27</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
